--- a/src/modules/excel/examples/data/test.xlsx
+++ b/src/modules/excel/examples/data/test.xlsx
@@ -859,7 +859,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="7" t="str">
-        <f>CONCATENATE(A6,', ',B6,'!')</f>
+        <f>CONCATENATE(A6,", ",B6,"!")</f>
         <v>Hello, World!</v>
       </c>
       <c r="E6" s="5"/>
